--- a/data/mini-example-resilience/Power_ImportExport.xlsx
+++ b/data/mini-example-resilience/Power_ImportExport.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98F9D03-711C-441F-B085-5ECBA5F4F64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C3E954-1B4A-4CEF-B8BD-CA15A4990E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -100,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="107">
   <si>
     <t>Power - Import/Export Hubs and Profiles</t>
   </si>
@@ -277,9 +290,6 @@
     <t>k0024</t>
   </si>
   <si>
-    <t>grid</t>
-  </si>
-  <si>
     <t>TestPackage2</t>
   </si>
   <si>
@@ -416,6 +426,15 @@
   </si>
   <si>
     <t>TestSource24</t>
+  </si>
+  <si>
+    <t>grid_imp</t>
+  </si>
+  <si>
+    <t>grid_exp</t>
+  </si>
+  <si>
+    <t>Node_feedin</t>
   </si>
 </sst>
 </file>
@@ -912,14 +931,18 @@
         <v>7</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="J3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -947,9 +970,15 @@
       <c r="I4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+      <c r="J4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
@@ -972,7 +1001,9 @@
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
+      <c r="J5" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
@@ -1001,9 +1032,15 @@
       <c r="I6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="J6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
@@ -1030,9 +1067,15 @@
       <c r="I7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
+      <c r="J7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
@@ -1049,17 +1092,23 @@
         <v>34</v>
       </c>
       <c r="G8" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H8" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I8" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J8" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K8" s="14">
+        <v>0</v>
+      </c>
+      <c r="L8" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" s="11"/>
@@ -1070,23 +1119,29 @@
         <v>35</v>
       </c>
       <c r="E9" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>60</v>
-      </c>
       <c r="G9" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H9" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I9" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J9" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K9" s="14">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="11"/>
@@ -1097,23 +1152,29 @@
         <v>36</v>
       </c>
       <c r="E10" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>62</v>
-      </c>
       <c r="G10" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H10" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I10" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J10" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K10" s="14">
+        <v>0</v>
+      </c>
+      <c r="L10" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11" s="11"/>
@@ -1124,23 +1185,29 @@
         <v>37</v>
       </c>
       <c r="E11" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>64</v>
-      </c>
       <c r="G11" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I11" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J11" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K11" s="14">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="11"/>
@@ -1151,23 +1218,29 @@
         <v>38</v>
       </c>
       <c r="E12" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="G12" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H12" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I12" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J12" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K12" s="14">
+        <v>0</v>
+      </c>
+      <c r="L12" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
@@ -1178,23 +1251,29 @@
         <v>39</v>
       </c>
       <c r="E13" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>68</v>
-      </c>
       <c r="G13" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I13" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J13" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K13" s="14">
+        <v>0</v>
+      </c>
+      <c r="L13" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="11"/>
@@ -1205,23 +1284,29 @@
         <v>40</v>
       </c>
       <c r="E14" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>70</v>
-      </c>
       <c r="G14" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H14" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I14" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J14" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K14" s="14">
+        <v>0</v>
+      </c>
+      <c r="L14" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15" s="11"/>
@@ -1232,23 +1317,29 @@
         <v>41</v>
       </c>
       <c r="E15" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>72</v>
-      </c>
       <c r="G15" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H15" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I15" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J15" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K15" s="14">
+        <v>0</v>
+      </c>
+      <c r="L15" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
@@ -1259,23 +1350,29 @@
         <v>42</v>
       </c>
       <c r="E16" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H16" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I16" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J16" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K16" s="14">
+        <v>0</v>
+      </c>
+      <c r="L16" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
@@ -1286,23 +1383,29 @@
         <v>43</v>
       </c>
       <c r="E17" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>76</v>
-      </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I17" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J17" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K17" s="14">
+        <v>0</v>
+      </c>
+      <c r="L17" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="11"/>
@@ -1313,23 +1416,29 @@
         <v>44</v>
       </c>
       <c r="E18" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>78</v>
-      </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I18" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J18" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K18" s="14">
+        <v>0</v>
+      </c>
+      <c r="L18" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="11"/>
@@ -1340,23 +1449,29 @@
         <v>45</v>
       </c>
       <c r="E19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="G19" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I19" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J19" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K19" s="14">
+        <v>0</v>
+      </c>
+      <c r="L19" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="11"/>
@@ -1367,23 +1482,29 @@
         <v>46</v>
       </c>
       <c r="E20" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H20" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I20" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J20" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K20" s="14">
+        <v>0</v>
+      </c>
+      <c r="L20" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="11"/>
@@ -1394,23 +1515,29 @@
         <v>47</v>
       </c>
       <c r="E21" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>84</v>
-      </c>
       <c r="G21" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I21" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J21" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K21" s="14">
+        <v>0</v>
+      </c>
+      <c r="L21" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
@@ -1421,23 +1548,29 @@
         <v>48</v>
       </c>
       <c r="E22" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>86</v>
-      </c>
       <c r="G22" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H22" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I22" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J22" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K22" s="14">
+        <v>0</v>
+      </c>
+      <c r="L22" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="11"/>
@@ -1448,23 +1581,29 @@
         <v>49</v>
       </c>
       <c r="E23" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>88</v>
-      </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H23" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I23" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J23" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K23" s="14">
+        <v>0</v>
+      </c>
+      <c r="L23" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="11"/>
@@ -1475,23 +1614,29 @@
         <v>50</v>
       </c>
       <c r="E24" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>90</v>
-      </c>
       <c r="G24" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H24" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I24" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J24" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K24" s="14">
+        <v>0</v>
+      </c>
+      <c r="L24" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="11"/>
@@ -1502,23 +1647,29 @@
         <v>51</v>
       </c>
       <c r="E25" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>92</v>
-      </c>
       <c r="G25" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H25" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I25" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J25" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K25" s="14">
+        <v>0</v>
+      </c>
+      <c r="L25" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
@@ -1529,23 +1680,29 @@
         <v>52</v>
       </c>
       <c r="E26" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>94</v>
-      </c>
       <c r="G26" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H26" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I26" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J26" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K26" s="14">
+        <v>0</v>
+      </c>
+      <c r="L26" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="11"/>
@@ -1556,23 +1713,29 @@
         <v>53</v>
       </c>
       <c r="E27" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="G27" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H27" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I27" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J27" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K27" s="14">
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="11"/>
@@ -1583,23 +1746,29 @@
         <v>54</v>
       </c>
       <c r="E28" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H28" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I28" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J28" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K28" s="14">
+        <v>0</v>
+      </c>
+      <c r="L28" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="11"/>
@@ -1610,23 +1779,29 @@
         <v>55</v>
       </c>
       <c r="E29" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>100</v>
-      </c>
       <c r="G29" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H29" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I29" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J29" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K29" s="14">
+        <v>0</v>
+      </c>
+      <c r="L29" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
@@ -1637,23 +1812,29 @@
         <v>56</v>
       </c>
       <c r="E30" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="G30" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H30" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I30" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J30" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K30" s="14">
+        <v>0</v>
+      </c>
+      <c r="L30" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
@@ -1664,23 +1845,29 @@
         <v>57</v>
       </c>
       <c r="E31" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>104</v>
-      </c>
       <c r="G31" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H31" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I31" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J31" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K31" s="14">
+        <v>0</v>
+      </c>
+      <c r="L31" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="11"/>

--- a/data/mini-example-resilience/Power_ImportExport.xlsx
+++ b/data/mini-example-resilience/Power_ImportExport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C3E954-1B4A-4CEF-B8BD-CA15A4990E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3879C6-5552-4F5A-AE4D-B120BF793C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="179">
   <si>
     <t>Power - Import/Export Hubs and Profiles</t>
   </si>
@@ -435,6 +435,222 @@
   </si>
   <si>
     <t>Node_feedin</t>
+  </si>
+  <si>
+    <t>k0025</t>
+  </si>
+  <si>
+    <t>TestPackage25</t>
+  </si>
+  <si>
+    <t>TestSource25</t>
+  </si>
+  <si>
+    <t>k0026</t>
+  </si>
+  <si>
+    <t>TestPackage26</t>
+  </si>
+  <si>
+    <t>TestSource26</t>
+  </si>
+  <si>
+    <t>k0027</t>
+  </si>
+  <si>
+    <t>TestPackage27</t>
+  </si>
+  <si>
+    <t>TestSource27</t>
+  </si>
+  <si>
+    <t>k0028</t>
+  </si>
+  <si>
+    <t>TestPackage28</t>
+  </si>
+  <si>
+    <t>TestSource28</t>
+  </si>
+  <si>
+    <t>k0029</t>
+  </si>
+  <si>
+    <t>TestPackage29</t>
+  </si>
+  <si>
+    <t>TestSource29</t>
+  </si>
+  <si>
+    <t>k0030</t>
+  </si>
+  <si>
+    <t>TestPackage30</t>
+  </si>
+  <si>
+    <t>TestSource30</t>
+  </si>
+  <si>
+    <t>k0031</t>
+  </si>
+  <si>
+    <t>TestPackage31</t>
+  </si>
+  <si>
+    <t>TestSource31</t>
+  </si>
+  <si>
+    <t>k0032</t>
+  </si>
+  <si>
+    <t>TestPackage32</t>
+  </si>
+  <si>
+    <t>TestSource32</t>
+  </si>
+  <si>
+    <t>k0033</t>
+  </si>
+  <si>
+    <t>TestPackage33</t>
+  </si>
+  <si>
+    <t>TestSource33</t>
+  </si>
+  <si>
+    <t>k0034</t>
+  </si>
+  <si>
+    <t>TestPackage34</t>
+  </si>
+  <si>
+    <t>TestSource34</t>
+  </si>
+  <si>
+    <t>k0035</t>
+  </si>
+  <si>
+    <t>TestPackage35</t>
+  </si>
+  <si>
+    <t>TestSource35</t>
+  </si>
+  <si>
+    <t>k0036</t>
+  </si>
+  <si>
+    <t>TestPackage36</t>
+  </si>
+  <si>
+    <t>TestSource36</t>
+  </si>
+  <si>
+    <t>k0037</t>
+  </si>
+  <si>
+    <t>TestPackage37</t>
+  </si>
+  <si>
+    <t>TestSource37</t>
+  </si>
+  <si>
+    <t>k0038</t>
+  </si>
+  <si>
+    <t>TestPackage38</t>
+  </si>
+  <si>
+    <t>TestSource38</t>
+  </si>
+  <si>
+    <t>k0039</t>
+  </si>
+  <si>
+    <t>TestPackage39</t>
+  </si>
+  <si>
+    <t>TestSource39</t>
+  </si>
+  <si>
+    <t>k0040</t>
+  </si>
+  <si>
+    <t>TestPackage40</t>
+  </si>
+  <si>
+    <t>TestSource40</t>
+  </si>
+  <si>
+    <t>k0041</t>
+  </si>
+  <si>
+    <t>TestPackage41</t>
+  </si>
+  <si>
+    <t>TestSource41</t>
+  </si>
+  <si>
+    <t>k0042</t>
+  </si>
+  <si>
+    <t>TestPackage42</t>
+  </si>
+  <si>
+    <t>TestSource42</t>
+  </si>
+  <si>
+    <t>k0043</t>
+  </si>
+  <si>
+    <t>TestPackage43</t>
+  </si>
+  <si>
+    <t>TestSource43</t>
+  </si>
+  <si>
+    <t>k0044</t>
+  </si>
+  <si>
+    <t>TestPackage44</t>
+  </si>
+  <si>
+    <t>TestSource44</t>
+  </si>
+  <si>
+    <t>k0045</t>
+  </si>
+  <si>
+    <t>TestPackage45</t>
+  </si>
+  <si>
+    <t>TestSource45</t>
+  </si>
+  <si>
+    <t>k0046</t>
+  </si>
+  <si>
+    <t>TestPackage46</t>
+  </si>
+  <si>
+    <t>TestSource46</t>
+  </si>
+  <si>
+    <t>k0047</t>
+  </si>
+  <si>
+    <t>TestPackage47</t>
+  </si>
+  <si>
+    <t>TestSource47</t>
+  </si>
+  <si>
+    <t>k0048</t>
+  </si>
+  <si>
+    <t>TestPackage48</t>
+  </si>
+  <si>
+    <t>TestSource48</t>
   </si>
 </sst>
 </file>
@@ -1871,315 +2087,795 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="15"/>
+      <c r="C32" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>2</v>
+      </c>
+      <c r="I32" s="15">
+        <v>40</v>
+      </c>
+      <c r="J32" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K32" s="14">
+        <v>0</v>
+      </c>
+      <c r="L32" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="15"/>
+      <c r="C33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>2</v>
+      </c>
+      <c r="I33" s="15">
+        <v>40</v>
+      </c>
+      <c r="J33" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K33" s="14">
+        <v>0</v>
+      </c>
+      <c r="L33" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="15"/>
+      <c r="C34" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>2</v>
+      </c>
+      <c r="I34" s="15">
+        <v>40</v>
+      </c>
+      <c r="J34" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K34" s="14">
+        <v>0</v>
+      </c>
+      <c r="L34" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="15"/>
+      <c r="C35" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>2</v>
+      </c>
+      <c r="I35" s="15">
+        <v>40</v>
+      </c>
+      <c r="J35" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K35" s="14">
+        <v>0</v>
+      </c>
+      <c r="L35" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="15"/>
+      <c r="C36" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>2</v>
+      </c>
+      <c r="I36" s="15">
+        <v>40</v>
+      </c>
+      <c r="J36" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K36" s="14">
+        <v>0</v>
+      </c>
+      <c r="L36" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="15"/>
+      <c r="C37" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>2</v>
+      </c>
+      <c r="I37" s="15">
+        <v>40</v>
+      </c>
+      <c r="J37" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K37" s="14">
+        <v>0</v>
+      </c>
+      <c r="L37" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="15"/>
+      <c r="C38" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>2</v>
+      </c>
+      <c r="I38" s="15">
+        <v>40</v>
+      </c>
+      <c r="J38" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K38" s="14">
+        <v>0</v>
+      </c>
+      <c r="L38" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="15"/>
+      <c r="C39" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>2</v>
+      </c>
+      <c r="I39" s="15">
+        <v>40</v>
+      </c>
+      <c r="J39" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K39" s="14">
+        <v>0</v>
+      </c>
+      <c r="L39" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="15"/>
+      <c r="C40" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>2</v>
+      </c>
+      <c r="I40" s="15">
+        <v>40</v>
+      </c>
+      <c r="J40" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K40" s="14">
+        <v>0</v>
+      </c>
+      <c r="L40" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="15"/>
+      <c r="C41" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>2</v>
+      </c>
+      <c r="I41" s="15">
+        <v>40</v>
+      </c>
+      <c r="J41" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K41" s="14">
+        <v>0</v>
+      </c>
+      <c r="L41" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="15"/>
+      <c r="C42" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>2</v>
+      </c>
+      <c r="I42" s="15">
+        <v>40</v>
+      </c>
+      <c r="J42" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K42" s="14">
+        <v>0</v>
+      </c>
+      <c r="L42" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="15"/>
+      <c r="C43" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>2</v>
+      </c>
+      <c r="I43" s="15">
+        <v>40</v>
+      </c>
+      <c r="J43" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K43" s="14">
+        <v>0</v>
+      </c>
+      <c r="L43" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="15"/>
+      <c r="C44" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>2</v>
+      </c>
+      <c r="I44" s="15">
+        <v>40</v>
+      </c>
+      <c r="J44" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K44" s="14">
+        <v>0</v>
+      </c>
+      <c r="L44" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="15"/>
+      <c r="C45" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>2</v>
+      </c>
+      <c r="I45" s="15">
+        <v>40</v>
+      </c>
+      <c r="J45" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K45" s="14">
+        <v>0</v>
+      </c>
+      <c r="L45" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="15"/>
+      <c r="C46" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>2</v>
+      </c>
+      <c r="I46" s="15">
+        <v>40</v>
+      </c>
+      <c r="J46" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K46" s="14">
+        <v>0</v>
+      </c>
+      <c r="L46" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="15"/>
+      <c r="C47" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>2</v>
+      </c>
+      <c r="I47" s="15">
+        <v>40</v>
+      </c>
+      <c r="J47" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K47" s="14">
+        <v>0</v>
+      </c>
+      <c r="L47" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="15"/>
+      <c r="C48" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>2</v>
+      </c>
+      <c r="I48" s="15">
+        <v>40</v>
+      </c>
+      <c r="J48" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K48" s="14">
+        <v>0</v>
+      </c>
+      <c r="L48" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="15"/>
+      <c r="C49" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>2</v>
+      </c>
+      <c r="I49" s="15">
+        <v>40</v>
+      </c>
+      <c r="J49" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K49" s="14">
+        <v>0</v>
+      </c>
+      <c r="L49" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="15"/>
+      <c r="C50" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>2</v>
+      </c>
+      <c r="I50" s="15">
+        <v>40</v>
+      </c>
+      <c r="J50" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K50" s="14">
+        <v>0</v>
+      </c>
+      <c r="L50" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="15"/>
+      <c r="C51" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>2</v>
+      </c>
+      <c r="I51" s="15">
+        <v>40</v>
+      </c>
+      <c r="J51" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K51" s="14">
+        <v>0</v>
+      </c>
+      <c r="L51" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="15"/>
+      <c r="C52" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>2</v>
+      </c>
+      <c r="I52" s="15">
+        <v>40</v>
+      </c>
+      <c r="J52" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K52" s="14">
+        <v>0</v>
+      </c>
+      <c r="L52" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="15"/>
+      <c r="C53" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>2</v>
+      </c>
+      <c r="I53" s="15">
+        <v>40</v>
+      </c>
+      <c r="J53" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K53" s="14">
+        <v>0</v>
+      </c>
+      <c r="L53" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="15"/>
+      <c r="C54" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>2</v>
+      </c>
+      <c r="I54" s="15">
+        <v>40</v>
+      </c>
+      <c r="J54" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K54" s="14">
+        <v>0</v>
+      </c>
+      <c r="L54" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="15"/>
+      <c r="C55" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>2</v>
+      </c>
+      <c r="I55" s="15">
+        <v>40</v>
+      </c>
+      <c r="J55" s="14">
+        <v>-2</v>
+      </c>
+      <c r="K55" s="14">
+        <v>0</v>
+      </c>
+      <c r="L55" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" s="11"/>
